--- a/static/standards-correlations/South_Carolina_CS1_State_Standards.xlsx
+++ b/static/standards-correlations/South_Carolina_CS1_State_Standards.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Crosswalk'!$A$4:$I$78</definedName>
@@ -565,10 +565,11 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scored against full lab bodies | C and Python tracks | Discovery Projects | SC CTE entry-level HS CS course | CTE course, not an academic standard set</t>
-        </is>
-      </c>
-    </row>
+          <t>Scored against full lab bodies | C and Python tracks | Introductory Projects | SC CTE entry-level HS CS course | CTE course, not an academic standard set</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -602,7 +603,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Discovery Projects</t>
+          <t>Introductory Projects</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -1039,7 +1040,7 @@
       </c>
       <c r="I17" s="11" t="inlineStr">
         <is>
-          <t>Ext 5.3E (Ethical Use and the Rules) works directly through unauthorised code reuse, what the school Acceptable Use Policy forbids, and why. Discovery Systems 10 adds manipulation and phishing.</t>
+          <t>Ext 5.3E (Ethical Use and the Rules) works directly through unauthorised code reuse, what the school Acceptable Use Policy forbids, and why. Introductory Systems 10 adds manipulation and phishing.</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1208,7 @@
       </c>
       <c r="I21" s="8" t="inlineStr">
         <is>
-          <t>Ext 1.1F (Why a PIN?), Ext 5.3G (Secret Messages / HTTPS) and Discovery Systems 10 cover weak credentials, exposed transport and phishing with avoidance methods. Extension-heavy and device threats are not surveyed.</t>
+          <t>Ext 1.1F (Why a PIN?), Ext 5.3G (Secret Messages / HTTPS) and Introductory Systems 10 cover weak credentials, exposed transport and phishing with avoidance methods. Extension-heavy and device threats are not surveyed.</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1549,7 @@
       </c>
       <c r="I32" s="8" t="inlineStr">
         <is>
-          <t>Competition runs are time-limited and Discovery Systems 13 assigns task ownership within a fixed window. Time management is practised, not instructed.</t>
+          <t>Competition runs are time-limited and Introductory Systems 13 assigns task ownership within a fixed window. Time management is practised, not instructed.</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2727,7 @@
       </c>
       <c r="I62" s="11" t="inlineStr">
         <is>
-          <t>Discovery Systems 4 teaches flowchart symbols and decision points, Ext 1.2B (Dependency Map) produces a structure diagram, and Unit 5.4 requires walking the algorithm through on paper before coding.</t>
+          <t>Introductory Systems 4 teaches flowchart symbols and decision points, Ext 1.2B (Dependency Map) produces a structure diagram, and Unit 5.4 requires walking the algorithm through on paper before coding.</t>
         </is>
       </c>
     </row>
@@ -3237,7 +3238,7 @@
       </c>
       <c r="I75" s="8" t="inlineStr">
         <is>
-          <t>Discovery Systems 10 covers phishing and Ext 5.3E (Ethical Use and the Rules) covers software piracy, two of the named threats. The remaining threat categories are not surveyed.</t>
+          <t>Introductory Systems 10 covers phishing and Ext 5.3E (Ethical Use and the Rules) covers software piracy, two of the named threats. The remaining threat categories are not surveyed.</t>
         </is>
       </c>
     </row>
@@ -3280,7 +3281,7 @@
       </c>
       <c r="I76" s="8" t="inlineStr">
         <is>
-          <t>Discovery Coding 2 covers what professional programmers actually do and Ext 5.3H (Find the Community) exposes students to practitioner work. Education routes, certifications and salaries are not researched.</t>
+          <t>Introductory Coding 2 covers what professional programmers actually do and Ext 5.3H (Find the Community) exposes students to practitioner work. Education routes, certifications and salaries are not researched.</t>
         </is>
       </c>
     </row>
@@ -3396,6 +3397,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
@@ -3440,7 +3442,7 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>Discovery Project, Coding strand, project NN (01-17).</t>
+          <t>Introductory Project, Coding strand, project NN (01-17).</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3454,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>Discovery Project, Systems strand, project NN (01-14).</t>
+          <t>Introductory Project, Systems strand, project NN (01-14).</t>
         </is>
       </c>
     </row>
@@ -3564,6 +3566,8 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
         <is>
@@ -3589,7 +3593,7 @@
 SOURCE NOTE: Codes and statements transcribed from the CodeHS published South Carolina Discovering Computer Science framework. Verify against the SCDE course standards document before any formal submission. SCDE contact for Computer Science 9-12 is listed publicly through the Office of Career and Technical Education.
 Crosswalk analysis (c) KIPR / Botball Explorer.
 === METHODOLOGY (revised) ===
-Scored against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Discovery projects.
+Scored against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Introductory projects.
 Scoring rule: Full requires evidence in the core lab flow. Partial is assigned where the only evidence sits in an optional Extension Challenge (labelled 'Finished early?'), or where the standard is only partly met.
 ADDITIONAL RULE FOR THIS FILE: employability dispositions in strand D are scored Partial where the curriculum creates the conditions in which the disposition is practised and visible, and blank where it does not. A curriculum cannot teach punctuality; it can require perseverance. That distinction is stated in each Coverage note rather than hidden in the score.</t>
         </is>
